--- a/artfynd/A 5728-2025 artfynd.xlsx
+++ b/artfynd/A 5728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91835455</v>
+        <v>91835462</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>796049.0891771642</v>
+        <v>796068</v>
       </c>
       <c r="R2" t="n">
-        <v>7464179.905072228</v>
+        <v>7464263</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91835456</v>
+        <v>91835448</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>796097.2004372245</v>
+        <v>796078</v>
       </c>
       <c r="R3" t="n">
-        <v>7464312.134483007</v>
+        <v>7464252</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2020-09-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91835448</v>
+        <v>91835449</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>796077.9693095597</v>
+        <v>796144</v>
       </c>
       <c r="R4" t="n">
-        <v>7464252.037582</v>
+        <v>7464416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2020-09-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91835466</v>
+        <v>91835455</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>796127.132759633</v>
+        <v>796049</v>
       </c>
       <c r="R5" t="n">
-        <v>7464349.913389249</v>
+        <v>7464180</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2020-09-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91835462</v>
+        <v>91835456</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>796068.1209240197</v>
+        <v>796097</v>
       </c>
       <c r="R6" t="n">
-        <v>7464263.090882384</v>
+        <v>7464312</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2020-09-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,6 +1157,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>91835466</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Granhult-avskrivet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>796127</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7464350</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-09-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-09-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5728-2025 artfynd.xlsx
+++ b/artfynd/A 5728-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835462</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835448</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835449</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835455</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835456</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835466</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>